--- a/Design/Excel/ET/Datas/Product/OrderConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/OrderConfig.xlsx
@@ -1128,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1252,6 +1252,28 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
